--- a/extenbooks/S903_extenbook.xlsx
+++ b/extenbooks/S903_extenbook.xlsx
@@ -30088,7 +30088,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**DPR** · **Phase**: 5 · **Series ID**: S903 · **Status**: ingested · **Authored**: 2026-05-18</t>
+          <t>**DPR** · **Phase**: 5 · **Series ID**: S903 · **Status**: book_period_validated · **Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
@@ -31778,11 +31778,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31805,76 +31805,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Actual Wage-Profit Curves, US 1947-1998</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S903_research.json", "adequacy_report": "Technical/docs/chapters/CH9_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S903_DPR.md", "epr": "Technical/docs/series/S903_EPR.md", "loader": "Technical/code/L01_loaders/L01_S903_load.py", "processor": "Technical/code/P02_processors/P02_S903_construct.py", "validator": "Technical/code/V03_validators/V03_S903_validate.py", "processed": "Technical/data/processed/S903.parquet", "chopped_csv": "Technical/chopped/S903.csv", "extenbook_xlsx": "Technical/extenbooks/S903_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T23:56:32.581279+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S903_extenbook.xlsx
+++ b/extenbooks/S903_extenbook.xlsx
@@ -31672,7 +31672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -31718,7 +31718,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -31758,12 +31758,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>anchor_checks</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S903", "n_anchors": 6, "n_red": 0, "n_green": 6, "n_na": 0, "anchors": [{"anchor_id": "S903_T918_1947", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1947. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 1.088, "actual": 1.088, "detail": "year=1947", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1958", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1958. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.9734, "actual": 0.9734, "detail": "year=1958", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1963", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1963. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.8547, "actual": 0.8547, "detail": "year=1963", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1967", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1967. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7644, "actual": 0.7644, "detail": "year=1967", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1972", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1972. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7033, "actual": 0.7033, "detail": "year=1972", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1998", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1998. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7317, "actual": 0.7317, "detail": "year=1998", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}]}, "splice_continuity": {"status": "NA", "sid": "S903", "splice_year": 1999, "detail": "no subseries spans 1998-&gt;1999"}, "level_plausibility": {"status": "NA", "sid": "S903", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:04:01.687104+00:00</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:26:26.311436+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S903_extenbook.xlsx
+++ b/extenbooks/S903_extenbook.xlsx
@@ -31763,7 +31763,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S903", "n_anchors": 6, "n_red": 0, "n_green": 6, "n_na": 0, "anchors": [{"anchor_id": "S903_T918_1947", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1947. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 1.088, "actual": 1.088, "detail": "year=1947", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1958", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1958. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.9734, "actual": 0.9734, "detail": "year=1958", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1963", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1963. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.8547, "actual": 0.8547, "detail": "year=1963", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1967", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1967. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7644, "actual": 0.7644, "detail": "year=1967", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1972", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1972. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7033, "actual": 0.7033, "detail": "year=1972", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1998", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1998. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7317, "actual": 0.7317, "detail": "year=1998", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}]}, "splice_continuity": {"status": "NA", "sid": "S903", "splice_year": 1999, "detail": "no subseries spans 1998-&gt;1999"}, "level_plausibility": {"status": "NA", "sid": "S903", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S903", "n_anchors": 6, "n_red": 0, "n_green": 6, "n_na": 0, "anchors": [{"anchor_id": "S903_T918_1947", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1947. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 1.088, "actual": 1.088, "detail": "year=1947", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1958", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1958. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.9734, "actual": 0.9734, "detail": "year=1958", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1963", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1963. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.8547, "actual": 0.8547, "detail": "year=1963", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1967", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1967. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7644, "actual": 0.7644, "detail": "year=1967", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1972", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1972. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7033, "actual": 0.7033, "detail": "year=1972", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S903_T918_1998", "anchor_type": "point", "subseries_id": "S903-R-FIXED", "source_description": "Table 9.18 maximum profit rate R (fixed-capital model), benchmark year 1998. Genuine non-circular anchor (S903-R-FIXED hand-checked EXACT, CH09_review).", "status": "GREEN", "expected": 0.7317, "actual": 0.7317, "detail": "year=1998", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}]}, "splice_continuity": {"status": "NA", "sid": "S903", "detail": "no extension / no book+extension ranges"}, "level_plausibility": {"status": "NA", "sid": "S903", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:26.311436+00:00</t>
+          <t>2026-07-11T03:44:26.793311+00:00</t>
         </is>
       </c>
     </row>
@@ -31790,11 +31790,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31817,6 +31817,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_9_PWT_BOOK2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh's actual (empirical) wage-profit curves, Figures 9.8, 9.12 and 9.19 (Ch9, Section X). For each US benchmark year the fixed-capital price system is solved for the wage share at each rate of profit (WSHARE), then rescaled by a Penn World Tables productivity index (PWT 7.1) into a real-wage curve (WRCURVE) plotted over its own profit-rate range up to that year's maximum profit rate (R). Construction-relevant: the empirical near-linear wage-profit curves that underpin Shaikh's transformation-problem and choice-of-technique arguments. Subseries carry genuinely different meanings and units (wage share, real-wage productivity index, productivity index, maximum profit rate), so units are split per subseries. NOTE: Figure 9.19's printed caption reads '1947-1972' and plots curves wr47-wr72 only, while the narrative (p.422) and this dataset cover 1947-1998; the display_name follows the data and text. SPARSE flag on S903-R-CIRC is a non-issue: it is a single scalar (one circulating-capital maximum profit rate), correctly one row.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S903_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S903_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PWT 7.1 variable confirmed as `rgdpwok` (Real GDP per worker, chain-weighted) in Appendix9_PennWorldTables.xlsx. 1947 anchor reconstructed by Shaikh from BEA Long Term Eco Growth A163 1948/1950. R_fixed values match Table 9.18 exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dimensionless_wage_share_and_real_wage_index</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
